--- a/AURA_MonteCarlo_Results_Detailed.xlsx
+++ b/AURA_MonteCarlo_Results_Detailed.xlsx
@@ -475,19 +475,19 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.93</v>
+        <v>3.97</v>
       </c>
       <c r="D2" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6002999999999999</v>
+        <v>0.596</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7579</v>
+        <v>0.7588</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0311</v>
+        <v>0.0364</v>
       </c>
     </row>
     <row r="3">
@@ -500,19 +500,19 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>5.46</v>
+        <v>5.48</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4147</v>
+        <v>0.409</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6274999999999999</v>
+        <v>0.623</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0015</v>
+        <v>0.0016</v>
       </c>
     </row>
     <row r="4">
@@ -525,16 +525,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="D4" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5653</v>
+        <v>0.5654</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7779</v>
+        <v>0.7839</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -550,16 +550,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="D5" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3198</v>
+        <v>0.323</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8002</v>
+        <v>0.8011</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -578,13 +578,13 @@
         <v>6.57</v>
       </c>
       <c r="D6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0014</v>
+        <v>0.0012</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2865</v>
+        <v>0.282</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -600,16 +600,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>5.4</v>
+        <v>5.44</v>
       </c>
       <c r="D7" t="n">
-        <v>3.49</v>
+        <v>3.53</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4215</v>
+        <v>0.4235</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5074</v>
+        <v>0.5082</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,19 +625,19 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>8.26</v>
+        <v>8.31</v>
       </c>
       <c r="D8" t="n">
-        <v>4.68</v>
+        <v>4.7</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2291</v>
+        <v>0.2287</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3411</v>
+        <v>0.337</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2881</v>
+        <v>0.2946</v>
       </c>
     </row>
     <row r="9">
@@ -650,16 +650,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>5.59</v>
+        <v>5.56</v>
       </c>
       <c r="D9" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="E9" t="n">
-        <v>0.305</v>
+        <v>0.3143</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4168</v>
+        <v>0.4188</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -678,13 +678,13 @@
         <v>6.93</v>
       </c>
       <c r="D10" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1411</v>
+        <v>0.137</v>
       </c>
       <c r="F10" t="n">
-        <v>0.355</v>
+        <v>0.3578</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.043</v>
+        <v>0.0434</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -725,19 +725,19 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.68</v>
       </c>
       <c r="D12" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0018</v>
+        <v>0.0019</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0779</v>
+        <v>0.0769</v>
       </c>
       <c r="G12" t="n">
-        <v>0.07679999999999999</v>
+        <v>0.07779999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -750,19 +750,19 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>11.06</v>
+        <v>11.04</v>
       </c>
       <c r="D13" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0091</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1011</v>
+        <v>0.0959</v>
       </c>
     </row>
     <row r="14">
@@ -775,10 +775,10 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>12.01</v>
+        <v>11.99</v>
       </c>
       <c r="D14" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5354</v>
+        <v>0.5319</v>
       </c>
     </row>
     <row r="15">
@@ -800,10 +800,10 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>13.9</v>
+        <v>13.88</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -812,7 +812,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9689</v>
+        <v>0.9638</v>
       </c>
     </row>
     <row r="16">
@@ -825,7 +825,7 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>14.85</v>
+        <v>14.84</v>
       </c>
       <c r="D16" t="n">
         <v>0.39</v>
@@ -837,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9971</v>
+        <v>0.998</v>
       </c>
     </row>
   </sheetData>
